--- a/TEF_Framework/Calculations/39 Bus/E calculation.xlsx
+++ b/TEF_Framework/Calculations/39 Bus/E calculation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\final year project\energy function\TEF_Framework\Calculations\39 Bus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\final year project\Final_Year_Project_BEL\TEF_Framework\Calculations\39 Bus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70F3350-A48B-4BDA-BCD9-3357C3421574}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E1414D-A94E-48A5-888F-393552ED77ED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9360" xr2:uid="{879DF73F-615F-46C8-BFB7-CD33A32BAA6E}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9360" xr2:uid="{879DF73F-615F-46C8-BFB7-CD33A32BAA6E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -449,7 +449,7 @@
     <col min="17" max="17" width="7.44140625" customWidth="1"/>
     <col min="18" max="18" width="15.44140625" customWidth="1"/>
     <col min="19" max="19" width="12.44140625" customWidth="1"/>
-    <col min="20" max="20" width="9.5546875" customWidth="1"/>
+    <col min="20" max="20" width="10.33203125" customWidth="1"/>
     <col min="21" max="21" width="12.33203125" customWidth="1"/>
     <col min="22" max="22" width="12.88671875" customWidth="1"/>
   </cols>
